--- a/assets/sdgym-leaderboard-files/Model_Details.xlsx
+++ b/assets/sdgym-leaderboard-files/Model_Details.xlsx
@@ -49,6 +49,18 @@
     <t>On the Pareto Curve</t>
   </si>
   <si>
+    <t>HMASynthesizer</t>
+  </si>
+  <si>
+    <t>HSASynthesizer</t>
+  </si>
+  <si>
+    <t>IndependentSynthesizer</t>
+  </si>
+  <si>
+    <t>MultiTableUniformSynthesizer</t>
+  </si>
+  <si>
     <t>BootstrapSynthesizer</t>
   </si>
   <si>
@@ -73,25 +85,25 @@
     <t>TVAESynthesizer</t>
   </si>
   <si>
+    <t>TabDDPMSynthesizer</t>
+  </si>
+  <si>
     <t>UniformSynthesizer</t>
   </si>
   <si>
     <t>XGCSynthesizer</t>
   </si>
   <si>
-    <t>ClavaDDPMSynthesizer</t>
-  </si>
-  <si>
-    <t>HMASynthesizer</t>
-  </si>
-  <si>
-    <t>HSASynthesizer</t>
-  </si>
-  <si>
-    <t>IndependentSynthesizer</t>
-  </si>
-  <si>
-    <t>MultiTableUniformSynthesizer</t>
+    <t>HMA</t>
+  </si>
+  <si>
+    <t>HSA</t>
+  </si>
+  <si>
+    <t>Independent</t>
+  </si>
+  <si>
+    <t>MultiTableUniform</t>
   </si>
   <si>
     <t>Bootstrap</t>
@@ -118,25 +130,16 @@
     <t>TVAE</t>
   </si>
   <si>
+    <t>TabDDPM</t>
+  </si>
+  <si>
     <t>Uniform</t>
   </si>
   <si>
     <t>XGC</t>
   </si>
   <si>
-    <t>ClavaDDPM</t>
-  </si>
-  <si>
-    <t>HMA</t>
-  </si>
-  <si>
-    <t>HSA</t>
-  </si>
-  <si>
-    <t>Independent</t>
-  </si>
-  <si>
-    <t>MultiTableUniform</t>
+    <t>multi_table</t>
   </si>
   <si>
     <t>single_table</t>
@@ -145,9 +148,6 @@
     <t>Unknown</t>
   </si>
   <si>
-    <t>multi_table</t>
-  </si>
-  <si>
     <t>sdv</t>
   </si>
   <si>
@@ -163,16 +163,32 @@
     <t>World Bank</t>
   </si>
   <si>
+    <t>Hierarchical Modeling</t>
+  </si>
+  <si>
+    <t>Hierarchical Sampling</t>
+  </si>
+  <si>
     <t>Statistical</t>
   </si>
   <si>
     <t>Deep Learning</t>
   </si>
   <si>
-    <t>Hierarchical Modeling</t>
-  </si>
-  <si>
-    <t>Hierarchical Sampling</t>
+    <t xml:space="preserve">The HMA Synthesizer uses hierarchical ML algorithm to learn from real data and generate synthetic data.  The algorithm uses classical statistics.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The HSA Synthesizer uses a segment-based algorithm to learn from your real data and generate synthetic data. This synthesizer offers fast performance for unlimited tables.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Independent Synthesizer learns each table's patterns independently. This synthesizer offers fast performance for unlimited tables.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multi-table baseline synthesizer that generates data uniformly at random for each table while preserving table schemas.
+</t>
   </si>
   <si>
     <t xml:space="preserve">The BootstrapSynthesizer is a synthesizer specifically designed to work when you only have a few rows of data. This synthesizer internally bootstraps your real data, and then uses the bootstrapped data to build a model.
@@ -207,30 +223,14 @@
 </t>
   </si>
   <si>
+    <t>No description available.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Statistical baseline synthesizer that generates values uniformly at random within the observed bounds of each column.
 </t>
   </si>
   <si>
     <t xml:space="preserve">The XGCSynthesizer stands for eXtraGaussianCopula. It uses classic, statistical methods to train a model and generate synthetic data similar to the GaussianCopulaSynthesizer. However, it contains some additional features for higher quality modeling.
-</t>
-  </si>
-  <si>
-    <t>No description available.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The HMA Synthesizer uses hierarchical ML algorithm to learn from real data and generate synthetic data.  The algorithm uses classical statistics.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The HSA Synthesizer uses a segment-based algorithm to learn from your real data and generate synthetic data. This synthesizer offers fast performance for unlimited tables.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Independent Synthesizer learns each table's patterns independently. This synthesizer offers fast performance for unlimited tables.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Multi-table baseline synthesizer that generates data uniformly at random for each table while preserving table schemas.
 </t>
   </si>
 </sst>
@@ -650,16 +650,16 @@
         <v>53</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="K2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -685,16 +685,16 @@
         <v>54</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="I3">
         <v>0</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -708,25 +708,25 @@
         <v>41</v>
       </c>
       <c r="D4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E4" t="s">
         <v>47</v>
       </c>
       <c r="F4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G4" t="s">
         <v>55</v>
       </c>
       <c r="H4">
-        <v>3</v>
+        <v>61</v>
       </c>
       <c r="I4">
         <v>0</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K4" t="b">
         <v>1</v>
@@ -743,28 +743,28 @@
         <v>41</v>
       </c>
       <c r="D5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E5" t="s">
         <v>47</v>
       </c>
       <c r="F5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G5" t="s">
         <v>56</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I5">
         <v>0</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -775,7 +775,7 @@
         <v>30</v>
       </c>
       <c r="C6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D6" t="s">
         <v>44</v>
@@ -784,13 +784,13 @@
         <v>47</v>
       </c>
       <c r="F6" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G6" t="s">
         <v>57</v>
       </c>
       <c r="H6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -810,22 +810,22 @@
         <v>31</v>
       </c>
       <c r="C7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G7" t="s">
         <v>58</v>
       </c>
       <c r="H7">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -845,22 +845,22 @@
         <v>32</v>
       </c>
       <c r="C8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E8" t="s">
         <v>47</v>
       </c>
       <c r="F8" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G8" t="s">
         <v>59</v>
       </c>
       <c r="H8">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -880,7 +880,7 @@
         <v>33</v>
       </c>
       <c r="C9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D9" t="s">
         <v>44</v>
@@ -889,13 +889,13 @@
         <v>47</v>
       </c>
       <c r="F9" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G9" t="s">
         <v>60</v>
       </c>
       <c r="H9">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -904,7 +904,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -915,22 +915,22 @@
         <v>34</v>
       </c>
       <c r="C10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E10" t="s">
         <v>47</v>
       </c>
       <c r="F10" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G10" t="s">
         <v>61</v>
       </c>
       <c r="H10">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -950,16 +950,16 @@
         <v>35</v>
       </c>
       <c r="C11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D11" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E11" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F11" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G11" t="s">
         <v>62</v>
@@ -991,25 +991,25 @@
         <v>44</v>
       </c>
       <c r="E12" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F12" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="G12" t="s">
         <v>63</v>
       </c>
       <c r="H12">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I12">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J12">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="K12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1020,7 +1020,7 @@
         <v>37</v>
       </c>
       <c r="C13" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D13" t="s">
         <v>44</v>
@@ -1029,22 +1029,22 @@
         <v>47</v>
       </c>
       <c r="F13" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G13" t="s">
         <v>64</v>
       </c>
       <c r="H13">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I13">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J13">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1061,25 +1061,25 @@
         <v>44</v>
       </c>
       <c r="E14" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="F14" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="G14" t="s">
         <v>65</v>
       </c>
       <c r="H14">
-        <v>46</v>
+        <v>3</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J14">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1090,28 +1090,28 @@
         <v>39</v>
       </c>
       <c r="C15" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D15" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E15" t="s">
         <v>47</v>
       </c>
       <c r="F15" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G15" t="s">
         <v>66</v>
       </c>
       <c r="H15">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="I15">
         <v>0</v>
       </c>
       <c r="J15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K15" t="b">
         <v>1</v>
@@ -1125,28 +1125,28 @@
         <v>40</v>
       </c>
       <c r="C16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E16" t="s">
         <v>47</v>
       </c>
       <c r="F16" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G16" t="s">
         <v>67</v>
       </c>
       <c r="H16">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I16">
         <v>0</v>
       </c>
       <c r="J16">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K16" t="b">
         <v>1</v>

--- a/assets/sdgym-leaderboard-files/Model_Details.xlsx
+++ b/assets/sdgym-leaderboard-files/Model_Details.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="72">
   <si>
     <t>Synthesizer</t>
   </si>
@@ -49,6 +49,42 @@
     <t>On the Pareto Curve</t>
   </si>
   <si>
+    <t>BootstrapSynthesizer</t>
+  </si>
+  <si>
+    <t>CTGANSynthesizer</t>
+  </si>
+  <si>
+    <t>ColumnSynthesizer</t>
+  </si>
+  <si>
+    <t>CopulaGANSynthesizer</t>
+  </si>
+  <si>
+    <t>GaussianCopulaSynthesizer</t>
+  </si>
+  <si>
+    <t>RealTabFormerSynthesizer</t>
+  </si>
+  <si>
+    <t>SegmentSynthesizer</t>
+  </si>
+  <si>
+    <t>TVAESynthesizer</t>
+  </si>
+  <si>
+    <t>TabDDPMSynthesizer</t>
+  </si>
+  <si>
+    <t>UniformSynthesizer</t>
+  </si>
+  <si>
+    <t>XGCSynthesizer</t>
+  </si>
+  <si>
+    <t>ClavaDDPMSynthesizer</t>
+  </si>
+  <si>
     <t>HMASynthesizer</t>
   </si>
   <si>
@@ -61,37 +97,40 @@
     <t>MultiTableUniformSynthesizer</t>
   </si>
   <si>
-    <t>BootstrapSynthesizer</t>
-  </si>
-  <si>
-    <t>CTGANSynthesizer</t>
-  </si>
-  <si>
-    <t>ColumnSynthesizer</t>
-  </si>
-  <si>
-    <t>CopulaGANSynthesizer</t>
-  </si>
-  <si>
-    <t>GaussianCopulaSynthesizer</t>
-  </si>
-  <si>
-    <t>RealTabFormerSynthesizer</t>
-  </si>
-  <si>
-    <t>SegmentSynthesizer</t>
-  </si>
-  <si>
-    <t>TVAESynthesizer</t>
-  </si>
-  <si>
-    <t>TabDDPMSynthesizer</t>
-  </si>
-  <si>
-    <t>UniformSynthesizer</t>
-  </si>
-  <si>
-    <t>XGCSynthesizer</t>
+    <t>Bootstrap</t>
+  </si>
+  <si>
+    <t>CTGAN</t>
+  </si>
+  <si>
+    <t>Column</t>
+  </si>
+  <si>
+    <t>CopulaGAN</t>
+  </si>
+  <si>
+    <t>GaussianCopula</t>
+  </si>
+  <si>
+    <t>RealTabFormer</t>
+  </si>
+  <si>
+    <t>Segment</t>
+  </si>
+  <si>
+    <t>TVAE</t>
+  </si>
+  <si>
+    <t>TabDDPM</t>
+  </si>
+  <si>
+    <t>Uniform</t>
+  </si>
+  <si>
+    <t>XGC</t>
+  </si>
+  <si>
+    <t>ClavaDDPM</t>
   </si>
   <si>
     <t>HMA</t>
@@ -106,48 +145,15 @@
     <t>MultiTableUniform</t>
   </si>
   <si>
-    <t>Bootstrap</t>
-  </si>
-  <si>
-    <t>CTGAN</t>
-  </si>
-  <si>
-    <t>Column</t>
-  </si>
-  <si>
-    <t>CopulaGAN</t>
-  </si>
-  <si>
-    <t>GaussianCopula</t>
-  </si>
-  <si>
-    <t>RealTabFormer</t>
-  </si>
-  <si>
-    <t>Segment</t>
-  </si>
-  <si>
-    <t>TVAE</t>
-  </si>
-  <si>
-    <t>TabDDPM</t>
-  </si>
-  <si>
-    <t>Uniform</t>
-  </si>
-  <si>
-    <t>XGC</t>
+    <t>single_table</t>
+  </si>
+  <si>
+    <t>Unknown</t>
   </si>
   <si>
     <t>multi_table</t>
   </si>
   <si>
-    <t>single_table</t>
-  </si>
-  <si>
-    <t>Unknown</t>
-  </si>
-  <si>
     <t>sdv</t>
   </si>
   <si>
@@ -163,16 +169,65 @@
     <t>World Bank</t>
   </si>
   <si>
+    <t>University of Waterloo, Vector Institute, Royal Bank of Canada</t>
+  </si>
+  <si>
+    <t>Statistical</t>
+  </si>
+  <si>
+    <t>Deep Learning</t>
+  </si>
+  <si>
     <t>Hierarchical Modeling</t>
   </si>
   <si>
     <t>Hierarchical Sampling</t>
   </si>
   <si>
-    <t>Statistical</t>
-  </si>
-  <si>
-    <t>Deep Learning</t>
+    <t xml:space="preserve">The BootstrapSynthesizer is a synthesizer specifically designed to work when you only have a few rows of data. This synthesizer internally bootstraps your real data, and then uses the bootstrapped data to build a model.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The CTGAN Synthesizer uses GAN-based, deep learning methods to train a model and generate synthetic data.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lightweight statistical synthesizer that applies simple, column-wise models without learning inter-column dependencies.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Copula GAN Synthesizer uses a mix classic, statistical methods and GAN-based deep learning methods to train a model and generate synthetic data.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Gaussian Copula Synthesizer uses classic, statistical methods to train a model and generate synthetic data.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transformer-based deep learning synthesizer that treats tabular data as a sequence modeling problem, inspired by large language models.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The SegmentSynthesizer calculates different segments of real data, and computes a different model for each one. You can supply any single-table synthesizer for computing the per-segment model. Use this when your real data is highly segmented, containing different patterns for each.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The TVAE Synthesizer uses a variational autoencoder (VAE)-based, neural network techniques to train a model and generate synthetic data.
+</t>
+  </si>
+  <si>
+    <t>No description available.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Statistical baseline synthesizer that generates values uniformly at random within the observed bounds of each column.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The XGCSynthesizer stands for eXtraGaussianCopula. It uses classic, statistical methods to train a model and generate synthetic data similar to the GaussianCopulaSynthesizer. However, it contains some additional features for higher quality modeling.
+</t>
+  </si>
+  <si>
+    <t>The ClavaDDPM model is an extension of the TabDDPM model to handle multi-table datasets. It is based on clustering labels as intermediaries to model relationships between tables, specifically focusing on foreign key constraints.</t>
   </si>
   <si>
     <t xml:space="preserve">The HMA Synthesizer uses hierarchical ML algorithm to learn from real data and generate synthetic data.  The algorithm uses classical statistics.
@@ -188,49 +243,6 @@
   </si>
   <si>
     <t xml:space="preserve">Multi-table baseline synthesizer that generates data uniformly at random for each table while preserving table schemas.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The BootstrapSynthesizer is a synthesizer specifically designed to work when you only have a few rows of data. This synthesizer internally bootstraps your real data, and then uses the bootstrapped data to build a model.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The CTGAN Synthesizer uses GAN-based, deep learning methods to train a model and generate synthetic data.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lightweight statistical synthesizer that applies simple, column-wise models without learning inter-column dependencies.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Copula GAN Synthesizer uses a mix classic, statistical methods and GAN-based deep learning methods to train a model and generate synthetic data.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Gaussian Copula Synthesizer uses classic, statistical methods to train a model and generate synthetic data.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transformer-based deep learning synthesizer that treats tabular data as a sequence modeling problem, inspired by large language models.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The SegmentSynthesizer calculates different segments of real data, and computes a different model for each one. You can supply any single-table synthesizer for computing the per-segment model. Use this when your real data is highly segmented, containing different patterns for each.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The TVAE Synthesizer uses a variational autoencoder (VAE)-based, neural network techniques to train a model and generate synthetic data.
-</t>
-  </si>
-  <si>
-    <t>No description available.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Statistical baseline synthesizer that generates values uniformly at random within the observed bounds of each column.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The XGCSynthesizer stands for eXtraGaussianCopula. It uses classic, statistical methods to train a model and generate synthetic data similar to the GaussianCopulaSynthesizer. However, it contains some additional features for higher quality modeling.
 </t>
   </si>
 </sst>
@@ -589,7 +601,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -632,34 +644,34 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="H2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="K2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -667,34 +679,34 @@
         <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F3" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G3" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="H3">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="I3">
         <v>0</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -702,31 +714,31 @@
         <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D4" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H4">
-        <v>61</v>
+        <v>2</v>
       </c>
       <c r="I4">
         <v>0</v>
       </c>
       <c r="J4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K4" t="b">
         <v>1</v>
@@ -737,34 +749,34 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="H5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I5">
         <v>0</v>
       </c>
       <c r="J5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -772,25 +784,25 @@
         <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E6" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G6" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="H6">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -807,34 +819,34 @@
         <v>16</v>
       </c>
       <c r="B7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D7" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E7" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G7" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="H7">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I7">
         <v>0</v>
       </c>
       <c r="J7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -842,25 +854,25 @@
         <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E8" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G8" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="H8">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -877,25 +889,25 @@
         <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D9" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E9" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G9" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="H9">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -904,7 +916,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -912,34 +924,34 @@
         <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C10" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D10" t="s">
+        <v>46</v>
+      </c>
+      <c r="E10" t="s">
         <v>44</v>
       </c>
-      <c r="E10" t="s">
-        <v>47</v>
-      </c>
       <c r="F10" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="G10" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="H10">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J10">
         <v>0</v>
       </c>
       <c r="K10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -947,25 +959,25 @@
         <v>20</v>
       </c>
       <c r="B11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D11" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F11" t="s">
         <v>52</v>
       </c>
       <c r="G11" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="H11">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -982,25 +994,25 @@
         <v>21</v>
       </c>
       <c r="B12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D12" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E12" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G12" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="H12">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -1017,34 +1029,34 @@
         <v>22</v>
       </c>
       <c r="B13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C13" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D13" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E13" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F13" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G13" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="H13">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="K13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1052,31 +1064,31 @@
         <v>23</v>
       </c>
       <c r="B14" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C14" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D14" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E14" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="F14" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="G14" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="H14">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="K14" t="b">
         <v>0</v>
@@ -1087,31 +1099,31 @@
         <v>24</v>
       </c>
       <c r="B15" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C15" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D15" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E15" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F15" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="G15" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H15">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="I15">
         <v>0</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K15" t="b">
         <v>1</v>
@@ -1122,33 +1134,68 @@
         <v>25</v>
       </c>
       <c r="B16" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C16" t="s">
+        <v>45</v>
+      </c>
+      <c r="D16" t="s">
+        <v>46</v>
+      </c>
+      <c r="E16" t="s">
+        <v>49</v>
+      </c>
+      <c r="F16" t="s">
+        <v>52</v>
+      </c>
+      <c r="G16" t="s">
+        <v>70</v>
+      </c>
+      <c r="H16">
+        <v>62</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>2</v>
+      </c>
+      <c r="K16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" t="s">
         <v>42</v>
       </c>
-      <c r="D16" t="s">
-        <v>44</v>
-      </c>
-      <c r="E16" t="s">
+      <c r="C17" t="s">
+        <v>45</v>
+      </c>
+      <c r="D17" t="s">
         <v>47</v>
       </c>
-      <c r="F16" t="s">
-        <v>51</v>
-      </c>
-      <c r="G16" t="s">
-        <v>67</v>
-      </c>
-      <c r="H16">
-        <v>4</v>
-      </c>
-      <c r="I16">
-        <v>0</v>
-      </c>
-      <c r="J16">
-        <v>0</v>
-      </c>
-      <c r="K16" t="b">
+      <c r="E17" t="s">
+        <v>49</v>
+      </c>
+      <c r="F17" t="s">
+        <v>52</v>
+      </c>
+      <c r="G17" t="s">
+        <v>71</v>
+      </c>
+      <c r="H17">
+        <v>2</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>6</v>
+      </c>
+      <c r="K17" t="b">
         <v>1</v>
       </c>
     </row>
